--- a/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ExportExcelTemplates/ReportSaleStudentProgress.xlsx
+++ b/Services/Fsel.Course/Fsel.Course.Lms.Api/Resources/ExportExcelTemplates/ReportSaleStudentProgress.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Backend\fsel_src\Services\Fsel.Course\Fsel.Course.Lms.Api\Resources\ExportExcelTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4627EF1A-ABDA-4445-8865-CED9CE757B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A729B96-0338-4A88-A802-BE09F5CECDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{FD04547B-C865-4C09-B5A3-F3A1A43AAEDA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FD04547B-C865-4C09-B5A3-F3A1A43AAEDA}"/>
   </bookViews>
   <sheets>
-    <sheet name="BC 1" sheetId="1" r:id="rId1"/>
-    <sheet name="BC 2" sheetId="2" r:id="rId2"/>
-    <sheet name="BC 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Còn hạn" sheetId="1" r:id="rId1"/>
+    <sheet name="Đã hết hạn" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BC 1'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Còn hạn'!$A$1:$AM$3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,63 +29,159 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="51">
   <si>
     <t>STT</t>
   </si>
   <si>
-    <t>Họ tên</t>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Trình độ PT</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Số khóa học</t>
+  </si>
+  <si>
+    <t>Thời gian dự kiến đạt nếu theo tiến trình chuẩn</t>
+  </si>
+  <si>
+    <t>Học sinh</t>
+  </si>
+  <si>
+    <t>PHHS</t>
+  </si>
+  <si>
+    <t>Nguồn data</t>
+  </si>
+  <si>
+    <t>Trường</t>
+  </si>
+  <si>
+    <t>Lớp</t>
+  </si>
+  <si>
+    <t>GV phụ trách</t>
+  </si>
+  <si>
+    <t>Quận</t>
+  </si>
+  <si>
+    <t>Tỉnh</t>
+  </si>
+  <si>
+    <t>Chưa đăng nhập</t>
+  </si>
+  <si>
+    <t>Chưa PT xong</t>
+  </si>
+  <si>
+    <t>PT mà chưa học</t>
+  </si>
+  <si>
+    <t>Chọn bài mà chưa học</t>
+  </si>
+  <si>
+    <t>Trình độ hiện tại</t>
+  </si>
+  <si>
+    <t>Gói học hiện tại</t>
+  </si>
+  <si>
+    <t>Số lần mua hàng</t>
+  </si>
+  <si>
+    <t>Ngày bắt đầu học</t>
+  </si>
+  <si>
+    <t>Ngày hết hạn</t>
+  </si>
+  <si>
+    <t>Lần cuối truy cập</t>
+  </si>
+  <si>
+    <t>Số ngày học còn lại</t>
+  </si>
+  <si>
+    <t>Số ngày không vào học</t>
+  </si>
+  <si>
+    <t>Số coins còn lại</t>
+  </si>
+  <si>
+    <t>Ngày bắt đầu khóa học</t>
+  </si>
+  <si>
+    <t>Khóa học hiện tại</t>
+  </si>
+  <si>
+    <t>Tiến độ hiện tại</t>
+  </si>
+  <si>
+    <t>IELTS</t>
+  </si>
+  <si>
+    <t>ACA</t>
+  </si>
+  <si>
+    <t>Học phần</t>
+  </si>
+  <si>
+    <t>Phần trăm</t>
+  </si>
+  <si>
+    <t>FMT 1</t>
+  </si>
+  <si>
+    <t>FMT 2</t>
+  </si>
+  <si>
+    <t>OA</t>
+  </si>
+  <si>
+    <t>Họ và tên</t>
+  </si>
+  <si>
+    <t>SĐT</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Lớp</t>
-  </si>
-  <si>
-    <t>Trình độ hiện tại</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>Khóa học</t>
-  </si>
-  <si>
-    <t>Mục tiêu đầu ra</t>
-  </si>
-  <si>
-    <t>Học phần</t>
-  </si>
-  <si>
-    <t>Phần trăm</t>
-  </si>
-  <si>
-    <t>Chưa đăng nhập</t>
-  </si>
-  <si>
-    <t>ĐN mà chưa PT</t>
-  </si>
-  <si>
-    <t>PT mà chưa học</t>
-  </si>
-  <si>
-    <t>Chọn bài mà chưa học</t>
-  </si>
-  <si>
-    <t>Tiến độ hiện tại</t>
-  </si>
-  <si>
-    <t>Ngày thanh toán</t>
-  </si>
-  <si>
-    <t>Ngày học đầu tiên</t>
-  </si>
-  <si>
-    <t>Ngày hết hạn</t>
-  </si>
-  <si>
-    <t>Số ngày chưa học  (từ lần cuối truy cập)</t>
+    <t>Năm sinh</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Target tuần</t>
+  </si>
+  <si>
+    <t>Số ngày đã hết hạn gói học, đã có order tính phí</t>
+  </si>
+  <si>
+    <t>4 tuần cuối</t>
+  </si>
+  <si>
+    <t>3 tuần cuối</t>
+  </si>
+  <si>
+    <t>2 tuần cuối</t>
+  </si>
+  <si>
+    <t>1 tuần cuối</t>
+  </si>
+  <si>
+    <t>Số Lần mua hàng</t>
+  </si>
+  <si>
+    <t>ACA/Ielts</t>
+  </si>
+  <si>
+    <t>Lesson đạt được</t>
   </si>
 </sst>
 </file>
@@ -115,7 +210,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,8 +229,20 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -147,22 +254,197 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -170,11 +452,79 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -187,11 +537,127 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -199,42 +665,198 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -551,335 +1173,633 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD27053-895B-43CB-83DD-8C405032EE4C}">
-  <dimension ref="A1:W7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AP3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.75" customWidth="1"/>
-    <col min="2" max="2" width="34.625" customWidth="1"/>
-    <col min="3" max="3" width="34.125" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="9" max="9" width="12.25" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
-    <col min="12" max="12" width="8.375" customWidth="1"/>
-    <col min="13" max="13" width="18.375" customWidth="1"/>
-    <col min="14" max="14" width="20.625" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="13" width="11.75" customWidth="1"/>
+    <col min="14" max="14" width="13.75" customWidth="1"/>
+    <col min="15" max="15" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:42" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="12"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="Q1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="R1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="S1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="7" t="s">
+      <c r="T1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="V1" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
+      <c r="W1" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB1" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC1" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD1" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE1" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI1" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ1" s="20"/>
+      <c r="AK1" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
     </row>
-    <row r="2" spans="1:23" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+    <row r="2" spans="1:42" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="19"/>
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="19"/>
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ2" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK2" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL2" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM2" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
+    <row r="3" spans="1:42" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="17"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="21"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="19"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="19"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
+      <c r="AH3" s="19"/>
+      <c r="AI3" s="19"/>
+      <c r="AJ3" s="19"/>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="M1:M2"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
+  <mergeCells count="36">
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="Z1:Z3"/>
+    <mergeCell ref="AF1:AF3"/>
+    <mergeCell ref="AE1:AE3"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="X1:X3"/>
+    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="Q1:Q3"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="R1:R3"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AA1:AA3"/>
+    <mergeCell ref="AB1:AB3"/>
+    <mergeCell ref="AC1:AC3"/>
+    <mergeCell ref="AG1:AG3"/>
+    <mergeCell ref="AH1:AH3"/>
+    <mergeCell ref="AD1:AD3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="G1:I2"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="W1:W3"/>
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="Y1:Y3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCACAE3-C422-4A1D-BFC5-B88C5BCE09F6}">
-  <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1908DD-BD0D-4828-85EC-1315A90721B0}">
+  <dimension ref="A1:BC3"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.125" customWidth="1"/>
-    <col min="2" max="2" width="29.375" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="5" width="16.625" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="8" max="8" width="14.125" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13.625" customWidth="1"/>
+    <col min="14" max="14" width="15.125" customWidth="1"/>
+    <col min="24" max="24" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:55" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="49"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="49"/>
+      <c r="M1" s="50"/>
+      <c r="N1" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="54" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" s="54" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="U1" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y1" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
+      <c r="Z1" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA1" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB1" s="39" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC1" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE1" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG1" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH1" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI1" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="23"/>
+      <c r="AL1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AM1" s="23"/>
+      <c r="AN1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO1" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP1" s="12"/>
+      <c r="AQ1" s="23"/>
+      <c r="AR1" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS1" s="12"/>
+      <c r="AT1" s="23"/>
+      <c r="AU1" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="12"/>
+      <c r="AW1" s="23"/>
+      <c r="AX1" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="AY1" s="12"/>
+      <c r="AZ1" s="13"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1"/>
+    <row r="2" spans="1:55" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="61"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="43"/>
+      <c r="AF2" s="30"/>
+      <c r="AG2" s="34"/>
+      <c r="AH2" s="30"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK2" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL2" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM2" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN2" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO2" s="24"/>
+      <c r="AP2" s="25"/>
+      <c r="AQ2" s="26"/>
+      <c r="AR2" s="24"/>
+      <c r="AS2" s="25"/>
+      <c r="AT2" s="26"/>
+      <c r="AU2" s="24"/>
+      <c r="AV2" s="25"/>
+      <c r="AW2" s="26"/>
+      <c r="AX2" s="24"/>
+      <c r="AY2" s="25"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I8" s="4"/>
+    <row r="3" spans="1:55" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="62"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="53"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="18"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="47"/>
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="38"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="44"/>
+      <c r="AF3" s="31"/>
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="35"/>
+      <c r="AK3" s="29"/>
+      <c r="AL3" s="29"/>
+      <c r="AM3" s="29"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AU3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AV3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AX3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93781CB-0036-4E6E-8124-4040E27BB92B}">
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="6.25" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="3" width="29.25" customWidth="1"/>
-    <col min="4" max="4" width="11.375" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
-    <col min="6" max="6" width="13.75" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="8" width="10.625" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-    </row>
-    <row r="2" spans="1:18" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+  <mergeCells count="41">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="X1:X3"/>
+    <mergeCell ref="Y1:Y3"/>
+    <mergeCell ref="Z1:Z3"/>
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="Q1:Q3"/>
+    <mergeCell ref="R1:R3"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="W1:W3"/>
+    <mergeCell ref="AA1:AA3"/>
+    <mergeCell ref="AB1:AB3"/>
+    <mergeCell ref="AC1:AC3"/>
+    <mergeCell ref="AD1:AD3"/>
+    <mergeCell ref="AE1:AE3"/>
+    <mergeCell ref="AF1:AF3"/>
+    <mergeCell ref="AG1:AG3"/>
+    <mergeCell ref="AH1:AH3"/>
+    <mergeCell ref="AI1:AI3"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AK2:AK3"/>
+    <mergeCell ref="AR1:AT2"/>
+    <mergeCell ref="AU1:AW2"/>
+    <mergeCell ref="AX1:AZ2"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AL2:AL3"/>
+    <mergeCell ref="AM2:AM3"/>
+    <mergeCell ref="AN2:AN3"/>
+    <mergeCell ref="AO1:AQ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
